--- a/Website_Übungssammlung.xlsx
+++ b/Website_Übungssammlung.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\carsteba\Nextcloud\Austausch_SOKO-L_Weiterentwicklung\Überarbeitung_Foliensätze\Block 7_SuS-Zusatzmodul\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9919E799-C4C3-4156-BC10-77E56731F928}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DD5F535F-966C-4042-BD83-875AC9089C70}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-76920" yWindow="-14415" windowWidth="77040" windowHeight="31920" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-76020" yWindow="-13515" windowWidth="57600" windowHeight="27840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Übersicht" sheetId="1" r:id="rId1"/>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="584" uniqueCount="442">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="589" uniqueCount="447">
   <si>
     <t>Hinweis: Dauern und Zielgruppenerweiterungen, die in den Ausgangstexten nicht eindeutig festgelegt waren, sind praxisorientierte Schätzungen. Die ausführlichen Anleitungen stehen im Blatt „Übungsabläufe“.</t>
   </si>
@@ -2701,6 +2701,21 @@
   </si>
   <si>
     <t>https://ggie.berkeley.edu/practice/honesty-commitment-for-students/</t>
+  </si>
+  <si>
+    <t>Emotionswissen</t>
+  </si>
+  <si>
+    <t>Emotionsregulation</t>
+  </si>
+  <si>
+    <t>Soziales Wissen</t>
+  </si>
+  <si>
+    <t>Beziehungsfertigkeiten</t>
+  </si>
+  <si>
+    <t>Verantwortungsvolle Entscheidungsfindung</t>
   </si>
 </sst>
 </file>
@@ -2868,18 +2883,9 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="2" applyAlignment="1"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -2891,13 +2897,37 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Link" xfId="2" builtinId="8"/>
     <cellStyle name="Normal" xfId="1" xr:uid="{00000000-0005-0000-0000-000000000000}"/>
     <cellStyle name="Standard" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="2">
+  <dxfs count="7">
+    <dxf>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
     <dxf>
       <font>
         <strike val="0"/>
@@ -2939,8 +2969,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="UebungenUebersicht" displayName="UebungenUebersicht" ref="A3:L50" totalsRowShown="0">
-  <tableColumns count="12">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="UebungenUebersicht" displayName="UebungenUebersicht" ref="A3:Q50" totalsRowShown="0">
+  <tableColumns count="17">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Übung"/>
     <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Kurzbeschreibung der Übung"/>
     <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="Dauer (ca.)"/>
@@ -2951,8 +2981,13 @@
     <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" name="Anwendungsfälle"/>
     <tableColumn id="6" xr3:uid="{00000000-0010-0000-0000-000006000000}" name="Benötigtes Material"/>
     <tableColumn id="7" xr3:uid="{00000000-0010-0000-0000-000007000000}" name="Lernziele"/>
-    <tableColumn id="8" xr3:uid="{76E72EB3-F2BA-41F7-AAEE-1EAB12470203}" name="Internetquelle" dataDxfId="1"/>
-    <tableColumn id="9" xr3:uid="{5D78A2DF-8BAA-41A2-B196-6D40A3D69338}" name="Originalquelle" dataDxfId="0"/>
+    <tableColumn id="17" xr3:uid="{1B0BB618-1984-4C0C-B170-E85C2E60A46E}" name="Emotionswissen" dataDxfId="0"/>
+    <tableColumn id="15" xr3:uid="{48024B56-A178-4174-B6CF-FE80AF7B4043}" name="Emotionsregulation" dataDxfId="2"/>
+    <tableColumn id="16" xr3:uid="{1BEF7C92-C9A5-4D9B-BA2D-4720A2273419}" name="Soziales Wissen" dataDxfId="1"/>
+    <tableColumn id="14" xr3:uid="{966C583F-E7F8-4F4A-ACFA-B9E143C79C45}" name="Beziehungsfertigkeiten" dataDxfId="3"/>
+    <tableColumn id="12" xr3:uid="{910601DA-CA66-4B2C-8B43-60EB6ADB6F70}" name="Verantwortungsvolle Entscheidungsfindung" dataDxfId="4"/>
+    <tableColumn id="8" xr3:uid="{76E72EB3-F2BA-41F7-AAEE-1EAB12470203}" name="Internetquelle" dataDxfId="6"/>
+    <tableColumn id="9" xr3:uid="{5D78A2DF-8BAA-41A2-B196-6D40A3D69338}" name="Originalquelle" dataDxfId="5"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -3165,7 +3200,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:L50"/>
+  <dimension ref="A1:Q50"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="61.25" bestFit="1" customWidth="1"/>
@@ -3173,44 +3208,54 @@
     <col min="3" max="3" width="23" customWidth="1"/>
     <col min="4" max="8" width="39" customWidth="1"/>
     <col min="9" max="9" width="33" customWidth="1"/>
-    <col min="10" max="10" width="42" customWidth="1"/>
-    <col min="11" max="11" width="27.625" customWidth="1"/>
-    <col min="12" max="12" width="26.75" customWidth="1"/>
+    <col min="10" max="15" width="42" customWidth="1"/>
+    <col min="16" max="16" width="27.625" customWidth="1"/>
+    <col min="17" max="17" width="26.75" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" ht="30" customHeight="1">
-      <c r="A1" s="7" t="s">
+    <row r="1" spans="1:17" ht="30" customHeight="1">
+      <c r="A1" s="15" t="s">
         <v>103</v>
       </c>
-      <c r="B1" s="7"/>
-      <c r="C1" s="7"/>
-      <c r="D1" s="7"/>
-      <c r="E1" s="7"/>
-      <c r="F1" s="7"/>
-      <c r="G1" s="7"/>
-      <c r="H1" s="7"/>
-      <c r="I1" s="7"/>
-      <c r="J1" s="7"/>
-      <c r="K1" s="7"/>
-      <c r="L1" s="7"/>
-    </row>
-    <row r="2" spans="1:12" ht="33.950000000000003" customHeight="1">
-      <c r="A2" s="11" t="s">
-        <v>0</v>
-      </c>
-      <c r="B2" s="11"/>
-      <c r="C2" s="11"/>
-      <c r="D2" s="11"/>
-      <c r="E2" s="11"/>
-      <c r="F2" s="11"/>
-      <c r="G2" s="11"/>
-      <c r="H2" s="11"/>
-      <c r="I2" s="11"/>
-      <c r="J2" s="11"/>
-      <c r="K2" s="11"/>
-      <c r="L2" s="11"/>
-    </row>
-    <row r="3" spans="1:12" ht="36" customHeight="1">
+      <c r="B1" s="15"/>
+      <c r="C1" s="15"/>
+      <c r="D1" s="15"/>
+      <c r="E1" s="15"/>
+      <c r="F1" s="15"/>
+      <c r="G1" s="15"/>
+      <c r="H1" s="15"/>
+      <c r="I1" s="15"/>
+      <c r="J1" s="15"/>
+      <c r="K1" s="15"/>
+      <c r="L1" s="15"/>
+      <c r="M1" s="15"/>
+      <c r="N1" s="15"/>
+      <c r="O1" s="15"/>
+      <c r="P1" s="15"/>
+      <c r="Q1" s="15"/>
+    </row>
+    <row r="2" spans="1:17" ht="33.950000000000003" customHeight="1">
+      <c r="A2" s="16" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="16"/>
+      <c r="C2" s="16"/>
+      <c r="D2" s="16"/>
+      <c r="E2" s="16"/>
+      <c r="F2" s="16"/>
+      <c r="G2" s="16"/>
+      <c r="H2" s="16"/>
+      <c r="I2" s="16"/>
+      <c r="J2" s="16"/>
+      <c r="K2" s="16"/>
+      <c r="L2" s="16"/>
+      <c r="M2" s="16"/>
+      <c r="N2" s="16"/>
+      <c r="O2" s="16"/>
+      <c r="P2" s="16"/>
+      <c r="Q2" s="16"/>
+    </row>
+    <row r="3" spans="1:17" ht="36" customHeight="1">
       <c r="A3" s="1" t="s">
         <v>177</v>
       </c>
@@ -3242,13 +3287,28 @@
         <v>6</v>
       </c>
       <c r="K3" s="1" t="s">
+        <v>442</v>
+      </c>
+      <c r="L3" s="1" t="s">
+        <v>443</v>
+      </c>
+      <c r="M3" s="1" t="s">
+        <v>444</v>
+      </c>
+      <c r="N3" s="1" t="s">
+        <v>445</v>
+      </c>
+      <c r="O3" s="1" t="s">
+        <v>446</v>
+      </c>
+      <c r="P3" s="1" t="s">
         <v>100</v>
       </c>
-      <c r="L3" s="1" t="s">
+      <c r="Q3" s="1" t="s">
         <v>102</v>
       </c>
     </row>
-    <row r="4" spans="1:12" ht="84" customHeight="1">
+    <row r="4" spans="1:17" ht="84" customHeight="1">
       <c r="A4" s="2" t="s">
         <v>178</v>
       </c>
@@ -3279,14 +3339,29 @@
       <c r="J4" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="K4" s="10" t="s">
+      <c r="K4" s="6">
+        <v>1</v>
+      </c>
+      <c r="L4" s="6">
+        <v>1</v>
+      </c>
+      <c r="M4" s="6">
+        <v>0</v>
+      </c>
+      <c r="N4" s="6">
+        <v>0</v>
+      </c>
+      <c r="O4" s="6">
+        <v>0</v>
+      </c>
+      <c r="P4" s="8" t="s">
         <v>101</v>
       </c>
-      <c r="L4" s="10" t="s">
+      <c r="Q4" s="8" t="s">
         <v>432</v>
       </c>
     </row>
-    <row r="5" spans="1:12" ht="84" customHeight="1">
+    <row r="5" spans="1:17" ht="84" customHeight="1">
       <c r="A5" s="2" t="s">
         <v>179</v>
       </c>
@@ -3317,14 +3392,29 @@
       <c r="J5" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="K5" s="10" t="s">
+      <c r="K5" s="6">
+        <v>1</v>
+      </c>
+      <c r="L5" s="6">
+        <v>1</v>
+      </c>
+      <c r="M5" s="6">
+        <v>0</v>
+      </c>
+      <c r="N5" s="6">
+        <v>0</v>
+      </c>
+      <c r="O5" s="6">
+        <v>0</v>
+      </c>
+      <c r="P5" s="8" t="s">
         <v>101</v>
       </c>
-      <c r="L5" s="10" t="s">
+      <c r="Q5" s="8" t="s">
         <v>429</v>
       </c>
     </row>
-    <row r="6" spans="1:12" ht="84" customHeight="1">
+    <row r="6" spans="1:17" ht="84" customHeight="1">
       <c r="A6" s="2" t="s">
         <v>180</v>
       </c>
@@ -3355,14 +3445,29 @@
       <c r="J6" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="K6" s="10" t="s">
+      <c r="K6" s="6">
+        <v>1</v>
+      </c>
+      <c r="L6" s="6">
+        <v>1</v>
+      </c>
+      <c r="M6" s="6">
+        <v>0</v>
+      </c>
+      <c r="N6" s="6">
+        <v>0</v>
+      </c>
+      <c r="O6" s="6">
+        <v>0</v>
+      </c>
+      <c r="P6" s="8" t="s">
         <v>101</v>
       </c>
-      <c r="L6" s="10" t="s">
+      <c r="Q6" s="8" t="s">
         <v>430</v>
       </c>
     </row>
-    <row r="7" spans="1:12" ht="84" customHeight="1">
+    <row r="7" spans="1:17" ht="84" customHeight="1">
       <c r="A7" s="2" t="s">
         <v>181</v>
       </c>
@@ -3393,14 +3498,29 @@
       <c r="J7" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="K7" s="10" t="s">
+      <c r="K7" s="6">
+        <v>1</v>
+      </c>
+      <c r="L7" s="6">
+        <v>1</v>
+      </c>
+      <c r="M7" s="6">
+        <v>0</v>
+      </c>
+      <c r="N7" s="6">
+        <v>0</v>
+      </c>
+      <c r="O7" s="6">
+        <v>0</v>
+      </c>
+      <c r="P7" s="8" t="s">
         <v>101</v>
       </c>
-      <c r="L7" s="10" t="s">
+      <c r="Q7" s="8" t="s">
         <v>431</v>
       </c>
     </row>
-    <row r="8" spans="1:12" ht="84" customHeight="1">
+    <row r="8" spans="1:17" ht="84" customHeight="1">
       <c r="A8" s="2" t="s">
         <v>182</v>
       </c>
@@ -3431,14 +3551,29 @@
       <c r="J8" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="K8" s="10" t="s">
+      <c r="K8" s="6">
+        <v>1</v>
+      </c>
+      <c r="L8" s="6">
+        <v>1</v>
+      </c>
+      <c r="M8" s="6">
+        <v>0</v>
+      </c>
+      <c r="N8" s="6">
+        <v>0</v>
+      </c>
+      <c r="O8" s="6">
+        <v>0</v>
+      </c>
+      <c r="P8" s="8" t="s">
         <v>101</v>
       </c>
-      <c r="L8" s="10" t="s">
+      <c r="Q8" s="8" t="s">
         <v>433</v>
       </c>
     </row>
-    <row r="9" spans="1:12" ht="84" customHeight="1">
+    <row r="9" spans="1:17" ht="84" customHeight="1">
       <c r="A9" s="2" t="s">
         <v>183</v>
       </c>
@@ -3469,14 +3604,29 @@
       <c r="J9" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="K9" s="10" t="s">
+      <c r="K9" s="6">
+        <v>0</v>
+      </c>
+      <c r="L9" s="6">
+        <v>0</v>
+      </c>
+      <c r="M9" s="6">
+        <v>1</v>
+      </c>
+      <c r="N9" s="6">
+        <v>1</v>
+      </c>
+      <c r="O9" s="6">
+        <v>1</v>
+      </c>
+      <c r="P9" s="8" t="s">
         <v>101</v>
       </c>
-      <c r="L9" s="10" t="s">
+      <c r="Q9" s="8" t="s">
         <v>434</v>
       </c>
     </row>
-    <row r="10" spans="1:12" ht="84" customHeight="1">
+    <row r="10" spans="1:17" ht="84" customHeight="1">
       <c r="A10" s="2" t="s">
         <v>184</v>
       </c>
@@ -3507,14 +3657,29 @@
       <c r="J10" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="K10" s="10" t="s">
+      <c r="K10" s="6">
+        <v>1</v>
+      </c>
+      <c r="L10" s="6">
+        <v>1</v>
+      </c>
+      <c r="M10" s="6">
+        <v>1</v>
+      </c>
+      <c r="N10" s="6">
+        <v>0</v>
+      </c>
+      <c r="O10" s="6">
+        <v>0</v>
+      </c>
+      <c r="P10" s="8" t="s">
         <v>101</v>
       </c>
-      <c r="L10" s="10" t="s">
+      <c r="Q10" s="8" t="s">
         <v>435</v>
       </c>
     </row>
-    <row r="11" spans="1:12" ht="84" customHeight="1">
+    <row r="11" spans="1:17" ht="84" customHeight="1">
       <c r="A11" s="2" t="s">
         <v>185</v>
       </c>
@@ -3545,14 +3710,29 @@
       <c r="J11" s="3" t="s">
         <v>53</v>
       </c>
-      <c r="K11" s="10" t="s">
+      <c r="K11" s="6">
+        <v>1</v>
+      </c>
+      <c r="L11" s="6">
+        <v>0</v>
+      </c>
+      <c r="M11" s="6">
+        <v>1</v>
+      </c>
+      <c r="N11" s="6">
+        <v>1</v>
+      </c>
+      <c r="O11" s="6">
+        <v>1</v>
+      </c>
+      <c r="P11" s="8" t="s">
         <v>101</v>
       </c>
-      <c r="L11" s="10" t="s">
+      <c r="Q11" s="8" t="s">
         <v>436</v>
       </c>
     </row>
-    <row r="12" spans="1:12" ht="84" customHeight="1">
+    <row r="12" spans="1:17" ht="84" customHeight="1">
       <c r="A12" s="2" t="s">
         <v>186</v>
       </c>
@@ -3583,14 +3763,29 @@
       <c r="J12" s="3" t="s">
         <v>58</v>
       </c>
-      <c r="K12" s="10" t="s">
+      <c r="K12" s="6">
+        <v>1</v>
+      </c>
+      <c r="L12" s="6">
+        <v>1</v>
+      </c>
+      <c r="M12" s="6">
+        <v>1</v>
+      </c>
+      <c r="N12" s="6">
+        <v>1</v>
+      </c>
+      <c r="O12" s="6">
+        <v>1</v>
+      </c>
+      <c r="P12" s="8" t="s">
         <v>101</v>
       </c>
-      <c r="L12" s="10" t="s">
+      <c r="Q12" s="8" t="s">
         <v>436</v>
       </c>
     </row>
-    <row r="13" spans="1:12" ht="84" customHeight="1">
+    <row r="13" spans="1:17" ht="84" customHeight="1">
       <c r="A13" s="4" t="s">
         <v>187</v>
       </c>
@@ -3621,18 +3816,33 @@
       <c r="J13" s="5" t="s">
         <v>64</v>
       </c>
-      <c r="K13" s="10" t="s">
+      <c r="K13" s="6">
+        <v>1</v>
+      </c>
+      <c r="L13" s="6">
+        <v>1</v>
+      </c>
+      <c r="M13" s="6">
+        <v>1</v>
+      </c>
+      <c r="N13" s="6">
+        <v>0</v>
+      </c>
+      <c r="O13" s="6">
+        <v>1</v>
+      </c>
+      <c r="P13" s="8" t="s">
         <v>101</v>
       </c>
-      <c r="L13" s="10" t="s">
+      <c r="Q13" s="8" t="s">
         <v>437</v>
       </c>
     </row>
-    <row r="14" spans="1:12" ht="156.75">
-      <c r="A14" s="9" t="s">
+    <row r="14" spans="1:17" ht="156.75">
+      <c r="A14" s="7" t="s">
         <v>331</v>
       </c>
-      <c r="B14" s="10" t="s">
+      <c r="B14" s="8" t="s">
         <v>191</v>
       </c>
       <c r="C14" t="s">
@@ -3647,24 +3857,39 @@
       <c r="G14">
         <v>0</v>
       </c>
-      <c r="H14" s="15" t="s">
+      <c r="H14" s="12" t="s">
         <v>340</v>
       </c>
       <c r="J14" t="s">
         <v>394</v>
       </c>
-      <c r="K14" s="10" t="s">
+      <c r="K14">
+        <v>1</v>
+      </c>
+      <c r="L14">
+        <v>1</v>
+      </c>
+      <c r="M14">
+        <v>1</v>
+      </c>
+      <c r="N14">
+        <v>1</v>
+      </c>
+      <c r="O14">
+        <v>0</v>
+      </c>
+      <c r="P14" s="8" t="s">
         <v>104</v>
       </c>
-      <c r="L14" s="10" t="s">
+      <c r="Q14" s="8" t="s">
         <v>428</v>
       </c>
     </row>
-    <row r="15" spans="1:12" ht="114">
-      <c r="A15" s="9" t="s">
+    <row r="15" spans="1:17" ht="114">
+      <c r="A15" s="7" t="s">
         <v>332</v>
       </c>
-      <c r="B15" s="10" t="s">
+      <c r="B15" s="8" t="s">
         <v>192</v>
       </c>
       <c r="C15" t="s">
@@ -3679,24 +3904,39 @@
       <c r="G15">
         <v>0</v>
       </c>
-      <c r="H15" s="15" t="s">
+      <c r="H15" s="12" t="s">
         <v>336</v>
       </c>
       <c r="J15" t="s">
         <v>391</v>
       </c>
-      <c r="K15" s="10" t="s">
+      <c r="K15">
+        <v>1</v>
+      </c>
+      <c r="L15">
+        <v>1</v>
+      </c>
+      <c r="M15">
+        <v>1</v>
+      </c>
+      <c r="N15">
+        <v>1</v>
+      </c>
+      <c r="O15">
+        <v>1</v>
+      </c>
+      <c r="P15" s="8" t="s">
         <v>105</v>
       </c>
-      <c r="L15" s="9" t="s">
+      <c r="Q15" s="7" t="s">
         <v>428</v>
       </c>
     </row>
-    <row r="16" spans="1:12" ht="185.25">
-      <c r="A16" s="9" t="s">
+    <row r="16" spans="1:17" ht="185.25">
+      <c r="A16" s="7" t="s">
         <v>333</v>
       </c>
-      <c r="B16" s="10" t="s">
+      <c r="B16" s="8" t="s">
         <v>193</v>
       </c>
       <c r="C16" t="s">
@@ -3711,7 +3951,7 @@
       <c r="G16">
         <v>0</v>
       </c>
-      <c r="H16" s="15" t="s">
+      <c r="H16" s="12" t="s">
         <v>337</v>
       </c>
       <c r="I16" t="s">
@@ -3720,18 +3960,33 @@
       <c r="J16" t="s">
         <v>392</v>
       </c>
-      <c r="K16" s="10" t="s">
+      <c r="K16">
+        <v>1</v>
+      </c>
+      <c r="L16">
+        <v>1</v>
+      </c>
+      <c r="M16">
+        <v>1</v>
+      </c>
+      <c r="N16">
+        <v>0</v>
+      </c>
+      <c r="O16">
+        <v>0</v>
+      </c>
+      <c r="P16" s="8" t="s">
         <v>106</v>
       </c>
-      <c r="L16" s="9" t="s">
+      <c r="Q16" s="7" t="s">
         <v>428</v>
       </c>
     </row>
-    <row r="17" spans="1:12" ht="114">
-      <c r="A17" s="9" t="s">
+    <row r="17" spans="1:17" ht="114">
+      <c r="A17" s="7" t="s">
         <v>334</v>
       </c>
-      <c r="B17" s="10" t="s">
+      <c r="B17" s="8" t="s">
         <v>194</v>
       </c>
       <c r="C17" t="s">
@@ -3746,7 +4001,7 @@
       <c r="G17">
         <v>0</v>
       </c>
-      <c r="H17" s="15" t="s">
+      <c r="H17" s="12" t="s">
         <v>338</v>
       </c>
       <c r="I17" t="s">
@@ -3755,18 +4010,33 @@
       <c r="J17" t="s">
         <v>393</v>
       </c>
-      <c r="K17" s="10" t="s">
+      <c r="K17">
+        <v>1</v>
+      </c>
+      <c r="L17">
+        <v>1</v>
+      </c>
+      <c r="M17">
+        <v>0</v>
+      </c>
+      <c r="N17">
+        <v>0</v>
+      </c>
+      <c r="O17">
+        <v>0</v>
+      </c>
+      <c r="P17" s="8" t="s">
         <v>107</v>
       </c>
-      <c r="L17" s="9" t="s">
+      <c r="Q17" s="7" t="s">
         <v>428</v>
       </c>
     </row>
-    <row r="18" spans="1:12" ht="57.75">
-      <c r="A18" s="9" t="s">
+    <row r="18" spans="1:17" ht="57.75">
+      <c r="A18" s="7" t="s">
         <v>140</v>
       </c>
-      <c r="B18" s="10" t="s">
+      <c r="B18" s="8" t="s">
         <v>195</v>
       </c>
       <c r="C18" t="s">
@@ -3775,33 +4045,48 @@
       <c r="E18">
         <v>1</v>
       </c>
-      <c r="F18" s="13">
-        <v>1</v>
-      </c>
-      <c r="G18" s="13">
-        <v>1</v>
-      </c>
-      <c r="H18" s="15" t="s">
+      <c r="F18" s="10">
+        <v>1</v>
+      </c>
+      <c r="G18" s="10">
+        <v>1</v>
+      </c>
+      <c r="H18" s="12" t="s">
         <v>341</v>
       </c>
       <c r="I18" t="s">
         <v>382</v>
       </c>
-      <c r="J18" s="15" t="s">
+      <c r="J18" s="12" t="s">
         <v>395</v>
       </c>
-      <c r="K18" s="10" t="s">
+      <c r="K18">
+        <v>1</v>
+      </c>
+      <c r="L18">
+        <v>0</v>
+      </c>
+      <c r="M18">
+        <v>0</v>
+      </c>
+      <c r="N18">
+        <v>0</v>
+      </c>
+      <c r="O18">
+        <v>0</v>
+      </c>
+      <c r="P18" s="8" t="s">
         <v>108</v>
       </c>
-      <c r="L18" s="9" t="s">
+      <c r="Q18" s="7" t="s">
         <v>428</v>
       </c>
     </row>
-    <row r="19" spans="1:12" ht="57.75">
-      <c r="A19" s="9" t="s">
+    <row r="19" spans="1:17" ht="57.75">
+      <c r="A19" s="7" t="s">
         <v>335</v>
       </c>
-      <c r="B19" s="10" t="s">
+      <c r="B19" s="8" t="s">
         <v>196</v>
       </c>
       <c r="C19" t="s">
@@ -3810,33 +4095,48 @@
       <c r="E19">
         <v>0</v>
       </c>
-      <c r="F19" s="13">
-        <v>1</v>
-      </c>
-      <c r="G19" s="13">
-        <v>1</v>
-      </c>
-      <c r="H19" s="15" t="s">
+      <c r="F19" s="10">
+        <v>1</v>
+      </c>
+      <c r="G19" s="10">
+        <v>1</v>
+      </c>
+      <c r="H19" s="12" t="s">
         <v>342</v>
       </c>
       <c r="I19" t="s">
         <v>371</v>
       </c>
-      <c r="J19" s="15" t="s">
+      <c r="J19" s="12" t="s">
         <v>396</v>
       </c>
-      <c r="K19" s="10" t="s">
+      <c r="K19">
+        <v>1</v>
+      </c>
+      <c r="L19">
+        <v>1</v>
+      </c>
+      <c r="M19">
+        <v>0</v>
+      </c>
+      <c r="N19">
+        <v>0</v>
+      </c>
+      <c r="O19">
+        <v>0</v>
+      </c>
+      <c r="P19" s="8" t="s">
         <v>109</v>
       </c>
-      <c r="L19" s="9" t="s">
+      <c r="Q19" s="7" t="s">
         <v>428</v>
       </c>
     </row>
-    <row r="20" spans="1:12" ht="100.5">
-      <c r="A20" s="9" t="s">
+    <row r="20" spans="1:17" ht="114.75">
+      <c r="A20" s="7" t="s">
         <v>141</v>
       </c>
-      <c r="B20" s="10" t="s">
+      <c r="B20" s="8" t="s">
         <v>197</v>
       </c>
       <c r="C20" t="s">
@@ -3845,13 +4145,13 @@
       <c r="E20">
         <v>0</v>
       </c>
-      <c r="F20" s="13">
-        <v>0</v>
-      </c>
-      <c r="G20" s="13">
-        <v>1</v>
-      </c>
-      <c r="H20" s="15" t="s">
+      <c r="F20" s="10">
+        <v>0</v>
+      </c>
+      <c r="G20" s="10">
+        <v>1</v>
+      </c>
+      <c r="H20" s="12" t="s">
         <v>343</v>
       </c>
       <c r="I20" t="s">
@@ -3860,18 +4160,33 @@
       <c r="J20" t="s">
         <v>397</v>
       </c>
-      <c r="K20" s="10" t="s">
+      <c r="K20">
+        <v>1</v>
+      </c>
+      <c r="L20">
+        <v>1</v>
+      </c>
+      <c r="M20">
+        <v>0</v>
+      </c>
+      <c r="N20">
+        <v>0</v>
+      </c>
+      <c r="O20">
+        <v>0</v>
+      </c>
+      <c r="P20" s="8" t="s">
         <v>110</v>
       </c>
-      <c r="L20" s="9" t="s">
+      <c r="Q20" s="7" t="s">
         <v>428</v>
       </c>
     </row>
-    <row r="21" spans="1:12" ht="143.25">
-      <c r="A21" s="9" t="s">
+    <row r="21" spans="1:17" ht="143.25">
+      <c r="A21" s="7" t="s">
         <v>142</v>
       </c>
-      <c r="B21" s="10" t="s">
+      <c r="B21" s="8" t="s">
         <v>198</v>
       </c>
       <c r="C21" t="s">
@@ -3880,33 +4195,48 @@
       <c r="E21">
         <v>1</v>
       </c>
-      <c r="F21" s="13">
-        <v>1</v>
-      </c>
-      <c r="G21" s="13">
-        <v>1</v>
-      </c>
-      <c r="H21" s="15" t="s">
+      <c r="F21" s="10">
+        <v>1</v>
+      </c>
+      <c r="G21" s="10">
+        <v>1</v>
+      </c>
+      <c r="H21" s="12" t="s">
         <v>344</v>
       </c>
       <c r="I21" t="s">
         <v>379</v>
       </c>
-      <c r="J21" s="15" t="s">
+      <c r="J21" s="12" t="s">
         <v>398</v>
       </c>
-      <c r="K21" s="10" t="s">
+      <c r="K21">
+        <v>0</v>
+      </c>
+      <c r="L21">
+        <v>0</v>
+      </c>
+      <c r="M21">
+        <v>1</v>
+      </c>
+      <c r="N21">
+        <v>1</v>
+      </c>
+      <c r="O21">
+        <v>0</v>
+      </c>
+      <c r="P21" s="8" t="s">
         <v>111</v>
       </c>
-      <c r="L21" s="9" t="s">
+      <c r="Q21" s="7" t="s">
         <v>428</v>
       </c>
     </row>
-    <row r="22" spans="1:12" ht="143.25">
-      <c r="A22" s="9" t="s">
+    <row r="22" spans="1:17" ht="143.25">
+      <c r="A22" s="7" t="s">
         <v>143</v>
       </c>
-      <c r="B22" s="10" t="s">
+      <c r="B22" s="8" t="s">
         <v>199</v>
       </c>
       <c r="C22" t="s">
@@ -3915,33 +4245,48 @@
       <c r="E22">
         <v>1</v>
       </c>
-      <c r="F22" s="13">
-        <v>1</v>
-      </c>
-      <c r="G22" s="13">
-        <v>1</v>
-      </c>
-      <c r="H22" s="15" t="s">
+      <c r="F22" s="10">
+        <v>1</v>
+      </c>
+      <c r="G22" s="10">
+        <v>1</v>
+      </c>
+      <c r="H22" s="12" t="s">
         <v>345</v>
       </c>
       <c r="I22" t="s">
         <v>383</v>
       </c>
-      <c r="J22" s="15" t="s">
+      <c r="J22" s="12" t="s">
         <v>399</v>
       </c>
-      <c r="K22" s="10" t="s">
+      <c r="K22">
+        <v>1</v>
+      </c>
+      <c r="L22">
+        <v>1</v>
+      </c>
+      <c r="M22">
+        <v>1</v>
+      </c>
+      <c r="N22">
+        <v>0</v>
+      </c>
+      <c r="O22">
+        <v>0</v>
+      </c>
+      <c r="P22" s="8" t="s">
         <v>112</v>
       </c>
-      <c r="L22" s="9" t="s">
+      <c r="Q22" s="7" t="s">
         <v>428</v>
       </c>
     </row>
-    <row r="23" spans="1:12" ht="129">
-      <c r="A23" s="9" t="s">
+    <row r="23" spans="1:17" ht="129">
+      <c r="A23" s="7" t="s">
         <v>144</v>
       </c>
-      <c r="B23" s="10" t="s">
+      <c r="B23" s="8" t="s">
         <v>200</v>
       </c>
       <c r="C23" t="s">
@@ -3950,33 +4295,48 @@
       <c r="E23">
         <v>0</v>
       </c>
-      <c r="F23" s="13">
-        <v>0</v>
-      </c>
-      <c r="G23" s="13">
-        <v>1</v>
-      </c>
-      <c r="H23" s="15" t="s">
+      <c r="F23" s="10">
+        <v>0</v>
+      </c>
+      <c r="G23" s="10">
+        <v>1</v>
+      </c>
+      <c r="H23" s="12" t="s">
         <v>346</v>
       </c>
-      <c r="I23" s="12" t="s">
+      <c r="I23" s="9" t="s">
         <v>401</v>
       </c>
-      <c r="J23" s="15" t="s">
+      <c r="J23" s="12" t="s">
         <v>400</v>
       </c>
-      <c r="K23" s="10" t="s">
+      <c r="K23">
+        <v>1</v>
+      </c>
+      <c r="L23">
+        <v>0</v>
+      </c>
+      <c r="M23">
+        <v>1</v>
+      </c>
+      <c r="N23">
+        <v>1</v>
+      </c>
+      <c r="O23">
+        <v>1</v>
+      </c>
+      <c r="P23" s="8" t="s">
         <v>113</v>
       </c>
-      <c r="L23" s="9" t="s">
+      <c r="Q23" s="7" t="s">
         <v>428</v>
       </c>
     </row>
-    <row r="24" spans="1:12" ht="86.25">
-      <c r="A24" s="9" t="s">
+    <row r="24" spans="1:17" ht="86.25">
+      <c r="A24" s="7" t="s">
         <v>145</v>
       </c>
-      <c r="B24" s="10" t="s">
+      <c r="B24" s="8" t="s">
         <v>201</v>
       </c>
       <c r="C24" t="s">
@@ -3985,33 +4345,48 @@
       <c r="E24">
         <v>0</v>
       </c>
-      <c r="F24" s="13">
-        <v>1</v>
-      </c>
-      <c r="G24" s="13">
-        <v>1</v>
-      </c>
-      <c r="H24" s="15" t="s">
+      <c r="F24" s="10">
+        <v>1</v>
+      </c>
+      <c r="G24" s="10">
+        <v>1</v>
+      </c>
+      <c r="H24" s="12" t="s">
         <v>347</v>
       </c>
       <c r="I24" t="s">
         <v>372</v>
       </c>
-      <c r="J24" s="15" t="s">
+      <c r="J24" s="12" t="s">
         <v>402</v>
       </c>
-      <c r="K24" s="10" t="s">
+      <c r="K24">
+        <v>1</v>
+      </c>
+      <c r="L24">
+        <v>1</v>
+      </c>
+      <c r="M24">
+        <v>1</v>
+      </c>
+      <c r="N24">
+        <v>0</v>
+      </c>
+      <c r="O24">
+        <v>0</v>
+      </c>
+      <c r="P24" s="8" t="s">
         <v>114</v>
       </c>
-      <c r="L24" s="9" t="s">
+      <c r="Q24" s="7" t="s">
         <v>428</v>
       </c>
     </row>
-    <row r="25" spans="1:12" ht="114.75">
-      <c r="A25" s="9" t="s">
+    <row r="25" spans="1:17" ht="114.75">
+      <c r="A25" s="7" t="s">
         <v>146</v>
       </c>
-      <c r="B25" s="10" t="s">
+      <c r="B25" s="8" t="s">
         <v>202</v>
       </c>
       <c r="C25" t="s">
@@ -4020,33 +4395,48 @@
       <c r="E25">
         <v>1</v>
       </c>
-      <c r="F25" s="13">
-        <v>1</v>
-      </c>
-      <c r="G25" s="13">
-        <v>1</v>
-      </c>
-      <c r="H25" s="15" t="s">
+      <c r="F25" s="10">
+        <v>1</v>
+      </c>
+      <c r="G25" s="10">
+        <v>1</v>
+      </c>
+      <c r="H25" s="12" t="s">
         <v>348</v>
       </c>
       <c r="I25" t="s">
         <v>373</v>
       </c>
-      <c r="J25" s="15" t="s">
+      <c r="J25" s="12" t="s">
         <v>403</v>
       </c>
-      <c r="K25" s="10" t="s">
+      <c r="K25">
+        <v>1</v>
+      </c>
+      <c r="L25">
+        <v>1</v>
+      </c>
+      <c r="M25">
+        <v>0</v>
+      </c>
+      <c r="N25">
+        <v>1</v>
+      </c>
+      <c r="O25">
+        <v>0</v>
+      </c>
+      <c r="P25" s="8" t="s">
         <v>115</v>
       </c>
-      <c r="L25" s="9" t="s">
+      <c r="Q25" s="7" t="s">
         <v>428</v>
       </c>
     </row>
-    <row r="26" spans="1:12" ht="43.5">
-      <c r="A26" s="9" t="s">
+    <row r="26" spans="1:17" ht="43.5">
+      <c r="A26" s="7" t="s">
         <v>147</v>
       </c>
-      <c r="B26" s="10" t="s">
+      <c r="B26" s="8" t="s">
         <v>203</v>
       </c>
       <c r="C26" t="s">
@@ -4055,33 +4445,48 @@
       <c r="E26">
         <v>1</v>
       </c>
-      <c r="F26" s="13">
-        <v>1</v>
-      </c>
-      <c r="G26" s="13">
-        <v>0</v>
-      </c>
-      <c r="H26" s="15" t="s">
+      <c r="F26" s="10">
+        <v>1</v>
+      </c>
+      <c r="G26" s="10">
+        <v>0</v>
+      </c>
+      <c r="H26" s="12" t="s">
         <v>349</v>
       </c>
       <c r="I26" t="s">
         <v>374</v>
       </c>
-      <c r="J26" s="15" t="s">
+      <c r="J26" s="12" t="s">
         <v>404</v>
       </c>
-      <c r="K26" s="10" t="s">
+      <c r="K26">
+        <v>1</v>
+      </c>
+      <c r="L26">
+        <v>1</v>
+      </c>
+      <c r="M26">
+        <v>0</v>
+      </c>
+      <c r="N26">
+        <v>0</v>
+      </c>
+      <c r="O26">
+        <v>0</v>
+      </c>
+      <c r="P26" s="8" t="s">
         <v>116</v>
       </c>
-      <c r="L26" s="9" t="s">
+      <c r="Q26" s="7" t="s">
         <v>428</v>
       </c>
     </row>
-    <row r="27" spans="1:12" ht="43.5">
-      <c r="A27" s="9" t="s">
+    <row r="27" spans="1:17" ht="43.5">
+      <c r="A27" s="7" t="s">
         <v>148</v>
       </c>
-      <c r="B27" s="10" t="s">
+      <c r="B27" s="8" t="s">
         <v>204</v>
       </c>
       <c r="C27" t="s">
@@ -4090,30 +4495,45 @@
       <c r="E27">
         <v>1</v>
       </c>
-      <c r="F27" s="13">
-        <v>1</v>
-      </c>
-      <c r="G27" s="13">
+      <c r="F27" s="10">
+        <v>1</v>
+      </c>
+      <c r="G27" s="10">
         <v>1</v>
       </c>
       <c r="I27" t="s">
         <v>384</v>
       </c>
-      <c r="J27" s="15" t="s">
+      <c r="J27" s="12" t="s">
         <v>405</v>
       </c>
-      <c r="K27" s="10" t="s">
+      <c r="K27">
+        <v>1</v>
+      </c>
+      <c r="L27">
+        <v>0</v>
+      </c>
+      <c r="M27">
+        <v>1</v>
+      </c>
+      <c r="N27">
+        <v>1</v>
+      </c>
+      <c r="O27">
+        <v>0</v>
+      </c>
+      <c r="P27" s="8" t="s">
         <v>117</v>
       </c>
-      <c r="L27" s="9" t="s">
+      <c r="Q27" s="7" t="s">
         <v>428</v>
       </c>
     </row>
-    <row r="28" spans="1:12" ht="57.75">
-      <c r="A28" s="9" t="s">
+    <row r="28" spans="1:17" ht="57.75">
+      <c r="A28" s="7" t="s">
         <v>149</v>
       </c>
-      <c r="B28" s="10" t="s">
+      <c r="B28" s="8" t="s">
         <v>205</v>
       </c>
       <c r="C28" t="s">
@@ -4122,33 +4542,48 @@
       <c r="E28">
         <v>1</v>
       </c>
-      <c r="F28" s="13">
-        <v>0</v>
-      </c>
-      <c r="G28" s="13">
-        <v>0</v>
-      </c>
-      <c r="H28" s="15" t="s">
+      <c r="F28" s="10">
+        <v>0</v>
+      </c>
+      <c r="G28" s="10">
+        <v>0</v>
+      </c>
+      <c r="H28" s="12" t="s">
         <v>350</v>
       </c>
       <c r="I28" t="s">
         <v>375</v>
       </c>
-      <c r="J28" s="15" t="s">
+      <c r="J28" s="12" t="s">
         <v>406</v>
       </c>
-      <c r="K28" s="17" t="s">
+      <c r="K28">
+        <v>1</v>
+      </c>
+      <c r="L28">
+        <v>1</v>
+      </c>
+      <c r="M28">
+        <v>1</v>
+      </c>
+      <c r="N28">
+        <v>1</v>
+      </c>
+      <c r="O28">
+        <v>1</v>
+      </c>
+      <c r="P28" s="14" t="s">
         <v>441</v>
       </c>
-      <c r="L28" s="9" t="s">
+      <c r="Q28" s="7" t="s">
         <v>428</v>
       </c>
     </row>
-    <row r="29" spans="1:12" ht="43.5">
-      <c r="A29" s="9" t="s">
+    <row r="29" spans="1:17" ht="43.5">
+      <c r="A29" s="7" t="s">
         <v>150</v>
       </c>
-      <c r="B29" s="10" t="s">
+      <c r="B29" s="8" t="s">
         <v>206</v>
       </c>
       <c r="C29" t="s">
@@ -4157,33 +4592,48 @@
       <c r="E29">
         <v>1</v>
       </c>
-      <c r="F29" s="13">
-        <v>1</v>
-      </c>
-      <c r="G29" s="13">
-        <v>0</v>
-      </c>
-      <c r="H29" s="15" t="s">
+      <c r="F29" s="10">
+        <v>1</v>
+      </c>
+      <c r="G29" s="10">
+        <v>0</v>
+      </c>
+      <c r="H29" s="12" t="s">
         <v>351</v>
       </c>
       <c r="I29" t="s">
         <v>375</v>
       </c>
-      <c r="J29" s="15" t="s">
+      <c r="J29" s="12" t="s">
         <v>407</v>
       </c>
-      <c r="K29" s="10" t="s">
+      <c r="K29">
+        <v>1</v>
+      </c>
+      <c r="L29">
+        <v>0</v>
+      </c>
+      <c r="M29">
+        <v>0</v>
+      </c>
+      <c r="N29">
+        <v>0</v>
+      </c>
+      <c r="O29">
+        <v>0</v>
+      </c>
+      <c r="P29" s="8" t="s">
         <v>118</v>
       </c>
-      <c r="L29" s="9" t="s">
+      <c r="Q29" s="7" t="s">
         <v>428</v>
       </c>
     </row>
-    <row r="30" spans="1:12" ht="143.25">
-      <c r="A30" s="9" t="s">
+    <row r="30" spans="1:17" ht="143.25">
+      <c r="A30" s="7" t="s">
         <v>151</v>
       </c>
-      <c r="B30" s="10" t="s">
+      <c r="B30" s="8" t="s">
         <v>207</v>
       </c>
       <c r="C30" t="s">
@@ -4192,33 +4642,48 @@
       <c r="E30">
         <v>1</v>
       </c>
-      <c r="F30" s="13">
-        <v>1</v>
-      </c>
-      <c r="G30" s="13">
-        <v>1</v>
-      </c>
-      <c r="H30" s="15" t="s">
+      <c r="F30" s="10">
+        <v>1</v>
+      </c>
+      <c r="G30" s="10">
+        <v>1</v>
+      </c>
+      <c r="H30" s="12" t="s">
         <v>352</v>
       </c>
       <c r="I30" t="s">
         <v>385</v>
       </c>
-      <c r="J30" s="15" t="s">
+      <c r="J30" s="12" t="s">
         <v>408</v>
       </c>
-      <c r="K30" s="10" t="s">
+      <c r="K30">
+        <v>1</v>
+      </c>
+      <c r="L30">
+        <v>0</v>
+      </c>
+      <c r="M30">
+        <v>1</v>
+      </c>
+      <c r="N30">
+        <v>0</v>
+      </c>
+      <c r="O30">
+        <v>0</v>
+      </c>
+      <c r="P30" s="8" t="s">
         <v>119</v>
       </c>
-      <c r="L30" s="9" t="s">
+      <c r="Q30" s="7" t="s">
         <v>428</v>
       </c>
     </row>
-    <row r="31" spans="1:12" ht="39">
-      <c r="A31" s="9" t="s">
+    <row r="31" spans="1:17" ht="39">
+      <c r="A31" s="7" t="s">
         <v>152</v>
       </c>
-      <c r="B31" s="10" t="s">
+      <c r="B31" s="8" t="s">
         <v>208</v>
       </c>
       <c r="C31" t="s">
@@ -4227,33 +4692,48 @@
       <c r="E31">
         <v>1</v>
       </c>
-      <c r="F31" s="13">
-        <v>0</v>
-      </c>
-      <c r="G31" s="13">
-        <v>0</v>
-      </c>
-      <c r="H31" s="15" t="s">
+      <c r="F31" s="10">
+        <v>0</v>
+      </c>
+      <c r="G31" s="10">
+        <v>0</v>
+      </c>
+      <c r="H31" s="12" t="s">
         <v>353</v>
       </c>
       <c r="I31" t="s">
         <v>376</v>
       </c>
-      <c r="J31" s="15" t="s">
+      <c r="J31" s="12" t="s">
         <v>409</v>
       </c>
-      <c r="K31" s="10" t="s">
+      <c r="K31">
+        <v>0</v>
+      </c>
+      <c r="L31">
+        <v>0</v>
+      </c>
+      <c r="M31">
+        <v>1</v>
+      </c>
+      <c r="N31">
+        <v>1</v>
+      </c>
+      <c r="O31">
+        <v>0</v>
+      </c>
+      <c r="P31" s="8" t="s">
         <v>120</v>
       </c>
-      <c r="L31" s="9" t="s">
+      <c r="Q31" s="7" t="s">
         <v>428</v>
       </c>
     </row>
-    <row r="32" spans="1:12" ht="51.75">
-      <c r="A32" s="9" t="s">
+    <row r="32" spans="1:17" ht="51.75">
+      <c r="A32" s="7" t="s">
         <v>153</v>
       </c>
-      <c r="B32" s="10" t="s">
+      <c r="B32" s="8" t="s">
         <v>209</v>
       </c>
       <c r="C32" t="s">
@@ -4262,10 +4742,10 @@
       <c r="E32">
         <v>1</v>
       </c>
-      <c r="F32" s="13">
-        <v>1</v>
-      </c>
-      <c r="G32" s="13">
+      <c r="F32" s="10">
+        <v>1</v>
+      </c>
+      <c r="G32" s="10">
         <v>1</v>
       </c>
       <c r="H32" t="s">
@@ -4274,21 +4754,36 @@
       <c r="I32" t="s">
         <v>386</v>
       </c>
-      <c r="J32" s="15" t="s">
+      <c r="J32" s="12" t="s">
         <v>410</v>
       </c>
-      <c r="K32" s="10" t="s">
+      <c r="K32">
+        <v>1</v>
+      </c>
+      <c r="L32">
+        <v>0</v>
+      </c>
+      <c r="M32">
+        <v>1</v>
+      </c>
+      <c r="N32">
+        <v>0</v>
+      </c>
+      <c r="O32">
+        <v>0</v>
+      </c>
+      <c r="P32" s="8" t="s">
         <v>121</v>
       </c>
-      <c r="L32" s="9" t="s">
+      <c r="Q32" s="7" t="s">
         <v>428</v>
       </c>
     </row>
-    <row r="33" spans="1:12" ht="100.5">
-      <c r="A33" s="9" t="s">
+    <row r="33" spans="1:17" ht="100.5">
+      <c r="A33" s="7" t="s">
         <v>154</v>
       </c>
-      <c r="B33" s="10" t="s">
+      <c r="B33" s="8" t="s">
         <v>210</v>
       </c>
       <c r="C33" t="s">
@@ -4297,33 +4792,48 @@
       <c r="E33">
         <v>1</v>
       </c>
-      <c r="F33" s="13">
-        <v>1</v>
-      </c>
-      <c r="G33" s="13">
-        <v>1</v>
-      </c>
-      <c r="H33" s="15" t="s">
+      <c r="F33" s="10">
+        <v>1</v>
+      </c>
+      <c r="G33" s="10">
+        <v>1</v>
+      </c>
+      <c r="H33" s="12" t="s">
         <v>355</v>
       </c>
       <c r="I33" t="s">
         <v>375</v>
       </c>
-      <c r="J33" s="15" t="s">
+      <c r="J33" s="12" t="s">
         <v>411</v>
       </c>
-      <c r="K33" s="10" t="s">
+      <c r="K33">
+        <v>1</v>
+      </c>
+      <c r="L33">
+        <v>1</v>
+      </c>
+      <c r="M33">
+        <v>1</v>
+      </c>
+      <c r="N33">
+        <v>1</v>
+      </c>
+      <c r="O33">
+        <v>0</v>
+      </c>
+      <c r="P33" s="8" t="s">
         <v>122</v>
       </c>
-      <c r="L33" s="9" t="s">
+      <c r="Q33" s="7" t="s">
         <v>428</v>
       </c>
     </row>
-    <row r="34" spans="1:12" ht="51.75">
-      <c r="A34" s="9" t="s">
+    <row r="34" spans="1:17" ht="51.75">
+      <c r="A34" s="7" t="s">
         <v>155</v>
       </c>
-      <c r="B34" s="10" t="s">
+      <c r="B34" s="8" t="s">
         <v>211</v>
       </c>
       <c r="C34" t="s">
@@ -4332,33 +4842,48 @@
       <c r="E34">
         <v>0</v>
       </c>
-      <c r="F34" s="13">
-        <v>1</v>
-      </c>
-      <c r="G34" s="13">
-        <v>0</v>
-      </c>
-      <c r="H34" s="15" t="s">
+      <c r="F34" s="10">
+        <v>1</v>
+      </c>
+      <c r="G34" s="10">
+        <v>0</v>
+      </c>
+      <c r="H34" s="12" t="s">
         <v>356</v>
       </c>
       <c r="I34" t="s">
         <v>377</v>
       </c>
-      <c r="J34" s="15" t="s">
+      <c r="J34" s="12" t="s">
         <v>412</v>
       </c>
-      <c r="K34" s="10" t="s">
+      <c r="K34">
+        <v>1</v>
+      </c>
+      <c r="L34">
+        <v>0</v>
+      </c>
+      <c r="M34">
+        <v>0</v>
+      </c>
+      <c r="N34">
+        <v>1</v>
+      </c>
+      <c r="O34">
+        <v>0</v>
+      </c>
+      <c r="P34" s="8" t="s">
         <v>123</v>
       </c>
-      <c r="L34" s="9" t="s">
+      <c r="Q34" s="7" t="s">
         <v>428</v>
       </c>
     </row>
-    <row r="35" spans="1:12" ht="51.75">
-      <c r="A35" s="9" t="s">
+    <row r="35" spans="1:17" ht="51.75">
+      <c r="A35" s="7" t="s">
         <v>156</v>
       </c>
-      <c r="B35" s="10" t="s">
+      <c r="B35" s="8" t="s">
         <v>212</v>
       </c>
       <c r="C35" t="s">
@@ -4367,33 +4892,48 @@
       <c r="E35">
         <v>1</v>
       </c>
-      <c r="F35" s="13">
-        <v>1</v>
-      </c>
-      <c r="G35" s="13">
-        <v>0</v>
-      </c>
-      <c r="H35" s="15" t="s">
+      <c r="F35" s="10">
+        <v>1</v>
+      </c>
+      <c r="G35" s="10">
+        <v>0</v>
+      </c>
+      <c r="H35" s="12" t="s">
         <v>357</v>
       </c>
       <c r="I35" t="s">
         <v>387</v>
       </c>
-      <c r="J35" s="15" t="s">
+      <c r="J35" s="12" t="s">
         <v>413</v>
       </c>
-      <c r="K35" s="10" t="s">
+      <c r="K35">
+        <v>1</v>
+      </c>
+      <c r="L35">
+        <v>1</v>
+      </c>
+      <c r="M35">
+        <v>0</v>
+      </c>
+      <c r="N35">
+        <v>0</v>
+      </c>
+      <c r="O35">
+        <v>0</v>
+      </c>
+      <c r="P35" s="8" t="s">
         <v>124</v>
       </c>
-      <c r="L35" s="9" t="s">
+      <c r="Q35" s="7" t="s">
         <v>428</v>
       </c>
     </row>
-    <row r="36" spans="1:12" ht="57.75">
-      <c r="A36" s="9" t="s">
+    <row r="36" spans="1:17" ht="57.75">
+      <c r="A36" s="7" t="s">
         <v>157</v>
       </c>
-      <c r="B36" s="10" t="s">
+      <c r="B36" s="8" t="s">
         <v>213</v>
       </c>
       <c r="C36" t="s">
@@ -4402,30 +4942,45 @@
       <c r="E36">
         <v>1</v>
       </c>
-      <c r="F36" s="13">
-        <v>1</v>
-      </c>
-      <c r="G36" s="13">
-        <v>1</v>
-      </c>
-      <c r="H36" s="15" t="s">
+      <c r="F36" s="10">
+        <v>1</v>
+      </c>
+      <c r="G36" s="10">
+        <v>1</v>
+      </c>
+      <c r="H36" s="12" t="s">
         <v>358</v>
       </c>
-      <c r="J36" s="15" t="s">
+      <c r="J36" s="12" t="s">
         <v>414</v>
       </c>
-      <c r="K36" s="10" t="s">
+      <c r="K36">
+        <v>1</v>
+      </c>
+      <c r="L36">
+        <v>1</v>
+      </c>
+      <c r="M36">
+        <v>0</v>
+      </c>
+      <c r="N36">
+        <v>0</v>
+      </c>
+      <c r="O36">
+        <v>0</v>
+      </c>
+      <c r="P36" s="8" t="s">
         <v>125</v>
       </c>
-      <c r="L36" s="9" t="s">
+      <c r="Q36" s="7" t="s">
         <v>428</v>
       </c>
     </row>
-    <row r="37" spans="1:12" ht="114.75">
-      <c r="A37" s="9" t="s">
+    <row r="37" spans="1:17" ht="114.75">
+      <c r="A37" s="7" t="s">
         <v>158</v>
       </c>
-      <c r="B37" s="10" t="s">
+      <c r="B37" s="8" t="s">
         <v>214</v>
       </c>
       <c r="C37" t="s">
@@ -4434,33 +4989,48 @@
       <c r="E37">
         <v>1</v>
       </c>
-      <c r="F37" s="13">
-        <v>0</v>
-      </c>
-      <c r="G37" s="13">
-        <v>0</v>
-      </c>
-      <c r="H37" s="15" t="s">
+      <c r="F37" s="10">
+        <v>0</v>
+      </c>
+      <c r="G37" s="10">
+        <v>0</v>
+      </c>
+      <c r="H37" s="12" t="s">
         <v>359</v>
       </c>
       <c r="I37" t="s">
         <v>378</v>
       </c>
-      <c r="J37" s="15" t="s">
+      <c r="J37" s="12" t="s">
         <v>415</v>
       </c>
-      <c r="K37" s="10" t="s">
+      <c r="K37">
+        <v>1</v>
+      </c>
+      <c r="L37">
+        <v>1</v>
+      </c>
+      <c r="M37">
+        <v>0</v>
+      </c>
+      <c r="N37">
+        <v>0</v>
+      </c>
+      <c r="O37">
+        <v>0</v>
+      </c>
+      <c r="P37" s="8" t="s">
         <v>126</v>
       </c>
-      <c r="L37" s="9" t="s">
+      <c r="Q37" s="7" t="s">
         <v>428</v>
       </c>
     </row>
-    <row r="38" spans="1:12" ht="143.25">
-      <c r="A38" s="9" t="s">
+    <row r="38" spans="1:17" ht="143.25">
+      <c r="A38" s="7" t="s">
         <v>159</v>
       </c>
-      <c r="B38" s="10" t="s">
+      <c r="B38" s="8" t="s">
         <v>215</v>
       </c>
       <c r="C38" t="s">
@@ -4469,33 +5039,48 @@
       <c r="E38">
         <v>1</v>
       </c>
-      <c r="F38" s="13">
-        <v>1</v>
-      </c>
-      <c r="G38" s="13">
-        <v>1</v>
-      </c>
-      <c r="H38" s="15" t="s">
+      <c r="F38" s="10">
+        <v>1</v>
+      </c>
+      <c r="G38" s="10">
+        <v>1</v>
+      </c>
+      <c r="H38" s="12" t="s">
         <v>360</v>
       </c>
       <c r="I38" t="s">
         <v>379</v>
       </c>
-      <c r="J38" s="15" t="s">
+      <c r="J38" s="12" t="s">
         <v>416</v>
       </c>
-      <c r="K38" s="10" t="s">
+      <c r="K38">
+        <v>1</v>
+      </c>
+      <c r="L38">
+        <v>0</v>
+      </c>
+      <c r="M38">
+        <v>1</v>
+      </c>
+      <c r="N38">
+        <v>0</v>
+      </c>
+      <c r="O38">
+        <v>0</v>
+      </c>
+      <c r="P38" s="8" t="s">
         <v>127</v>
       </c>
-      <c r="L38" s="9" t="s">
+      <c r="Q38" s="7" t="s">
         <v>428</v>
       </c>
     </row>
-    <row r="39" spans="1:12" ht="51.75">
-      <c r="A39" s="9" t="s">
+    <row r="39" spans="1:17" ht="51.75">
+      <c r="A39" s="7" t="s">
         <v>160</v>
       </c>
-      <c r="B39" s="10" t="s">
+      <c r="B39" s="8" t="s">
         <v>216</v>
       </c>
       <c r="C39" t="s">
@@ -4504,33 +5089,48 @@
       <c r="E39">
         <v>1</v>
       </c>
-      <c r="F39" s="13">
-        <v>1</v>
-      </c>
-      <c r="G39" s="13">
-        <v>0</v>
-      </c>
-      <c r="H39" s="15" t="s">
+      <c r="F39" s="10">
+        <v>1</v>
+      </c>
+      <c r="G39" s="10">
+        <v>0</v>
+      </c>
+      <c r="H39" s="12" t="s">
         <v>351</v>
       </c>
       <c r="I39" t="s">
         <v>375</v>
       </c>
-      <c r="J39" s="15" t="s">
+      <c r="J39" s="12" t="s">
         <v>417</v>
       </c>
-      <c r="K39" s="10" t="s">
+      <c r="K39">
+        <v>1</v>
+      </c>
+      <c r="L39">
+        <v>1</v>
+      </c>
+      <c r="M39">
+        <v>0</v>
+      </c>
+      <c r="N39">
+        <v>0</v>
+      </c>
+      <c r="O39">
+        <v>0</v>
+      </c>
+      <c r="P39" s="8" t="s">
         <v>128</v>
       </c>
-      <c r="L39" s="9" t="s">
+      <c r="Q39" s="7" t="s">
         <v>428</v>
       </c>
     </row>
-    <row r="40" spans="1:12" ht="72">
-      <c r="A40" s="9" t="s">
+    <row r="40" spans="1:17" ht="72">
+      <c r="A40" s="7" t="s">
         <v>161</v>
       </c>
-      <c r="B40" s="10" t="s">
+      <c r="B40" s="8" t="s">
         <v>217</v>
       </c>
       <c r="C40" t="s">
@@ -4539,13 +5139,13 @@
       <c r="E40">
         <v>1</v>
       </c>
-      <c r="F40" s="13">
-        <v>1</v>
-      </c>
-      <c r="G40" s="13">
-        <v>1</v>
-      </c>
-      <c r="H40" s="15" t="s">
+      <c r="F40" s="10">
+        <v>1</v>
+      </c>
+      <c r="G40" s="10">
+        <v>1</v>
+      </c>
+      <c r="H40" s="12" t="s">
         <v>361</v>
       </c>
       <c r="I40" t="s">
@@ -4554,18 +5154,33 @@
       <c r="J40" t="s">
         <v>418</v>
       </c>
-      <c r="K40" s="10" t="s">
+      <c r="K40">
+        <v>1</v>
+      </c>
+      <c r="L40">
+        <v>1</v>
+      </c>
+      <c r="M40">
+        <v>0</v>
+      </c>
+      <c r="N40">
+        <v>0</v>
+      </c>
+      <c r="O40">
+        <v>0</v>
+      </c>
+      <c r="P40" s="8" t="s">
         <v>129</v>
       </c>
-      <c r="L40" s="9" t="s">
+      <c r="Q40" s="7" t="s">
         <v>428</v>
       </c>
     </row>
-    <row r="41" spans="1:12" ht="100.5">
-      <c r="A41" s="9" t="s">
+    <row r="41" spans="1:17" ht="100.5">
+      <c r="A41" s="7" t="s">
         <v>162</v>
       </c>
-      <c r="B41" s="10" t="s">
+      <c r="B41" s="8" t="s">
         <v>218</v>
       </c>
       <c r="C41" t="s">
@@ -4574,33 +5189,48 @@
       <c r="E41">
         <v>1</v>
       </c>
-      <c r="F41" s="13">
-        <v>0</v>
-      </c>
-      <c r="G41" s="13">
-        <v>0</v>
-      </c>
-      <c r="H41" s="15" t="s">
+      <c r="F41" s="10">
+        <v>0</v>
+      </c>
+      <c r="G41" s="10">
+        <v>0</v>
+      </c>
+      <c r="H41" s="12" t="s">
         <v>339</v>
       </c>
       <c r="I41" t="s">
         <v>380</v>
       </c>
-      <c r="J41" s="15" t="s">
+      <c r="J41" s="12" t="s">
         <v>419</v>
       </c>
-      <c r="K41" s="10" t="s">
+      <c r="K41">
+        <v>1</v>
+      </c>
+      <c r="L41">
+        <v>1</v>
+      </c>
+      <c r="M41">
+        <v>0</v>
+      </c>
+      <c r="N41">
+        <v>0</v>
+      </c>
+      <c r="O41">
+        <v>0</v>
+      </c>
+      <c r="P41" s="8" t="s">
         <v>130</v>
       </c>
-      <c r="L41" s="9" t="s">
+      <c r="Q41" s="7" t="s">
         <v>428</v>
       </c>
     </row>
-    <row r="42" spans="1:12" ht="129">
-      <c r="A42" s="9" t="s">
+    <row r="42" spans="1:17" ht="129">
+      <c r="A42" s="7" t="s">
         <v>163</v>
       </c>
-      <c r="B42" s="10" t="s">
+      <c r="B42" s="8" t="s">
         <v>219</v>
       </c>
       <c r="C42" t="s">
@@ -4609,33 +5239,48 @@
       <c r="E42">
         <v>1</v>
       </c>
-      <c r="F42" s="13">
-        <v>0</v>
-      </c>
-      <c r="G42" s="13">
-        <v>0</v>
-      </c>
-      <c r="H42" s="15" t="s">
+      <c r="F42" s="10">
+        <v>0</v>
+      </c>
+      <c r="G42" s="10">
+        <v>0</v>
+      </c>
+      <c r="H42" s="12" t="s">
         <v>362</v>
       </c>
       <c r="I42" t="s">
         <v>389</v>
       </c>
-      <c r="J42" s="15" t="s">
+      <c r="J42" s="12" t="s">
         <v>420</v>
       </c>
-      <c r="K42" s="10" t="s">
+      <c r="K42">
+        <v>1</v>
+      </c>
+      <c r="L42">
+        <v>1</v>
+      </c>
+      <c r="M42">
+        <v>0</v>
+      </c>
+      <c r="N42">
+        <v>0</v>
+      </c>
+      <c r="O42">
+        <v>0</v>
+      </c>
+      <c r="P42" s="8" t="s">
         <v>131</v>
       </c>
-      <c r="L42" s="9" t="s">
+      <c r="Q42" s="7" t="s">
         <v>428</v>
       </c>
     </row>
-    <row r="43" spans="1:12" ht="114.75">
-      <c r="A43" s="9" t="s">
+    <row r="43" spans="1:17" ht="114.75">
+      <c r="A43" s="7" t="s">
         <v>164</v>
       </c>
-      <c r="B43" s="10" t="s">
+      <c r="B43" s="8" t="s">
         <v>220</v>
       </c>
       <c r="C43" t="s">
@@ -4644,33 +5289,48 @@
       <c r="E43">
         <v>1</v>
       </c>
-      <c r="F43" s="13">
-        <v>1</v>
-      </c>
-      <c r="G43" s="13">
-        <v>1</v>
-      </c>
-      <c r="H43" s="15" t="s">
+      <c r="F43" s="10">
+        <v>1</v>
+      </c>
+      <c r="G43" s="10">
+        <v>1</v>
+      </c>
+      <c r="H43" s="12" t="s">
         <v>363</v>
       </c>
       <c r="I43" t="s">
         <v>381</v>
       </c>
-      <c r="J43" s="15" t="s">
+      <c r="J43" s="12" t="s">
         <v>421</v>
       </c>
-      <c r="K43" s="10" t="s">
+      <c r="K43">
+        <v>1</v>
+      </c>
+      <c r="L43">
+        <v>0</v>
+      </c>
+      <c r="M43">
+        <v>0</v>
+      </c>
+      <c r="N43">
+        <v>0</v>
+      </c>
+      <c r="O43">
+        <v>0</v>
+      </c>
+      <c r="P43" s="8" t="s">
         <v>132</v>
       </c>
-      <c r="L43" s="9" t="s">
+      <c r="Q43" s="7" t="s">
         <v>428</v>
       </c>
     </row>
-    <row r="44" spans="1:12" ht="72">
-      <c r="A44" s="9" t="s">
+    <row r="44" spans="1:17" ht="72">
+      <c r="A44" s="7" t="s">
         <v>165</v>
       </c>
-      <c r="B44" s="10" t="s">
+      <c r="B44" s="8" t="s">
         <v>227</v>
       </c>
       <c r="C44" t="s">
@@ -4679,13 +5339,13 @@
       <c r="E44">
         <v>0</v>
       </c>
-      <c r="F44" s="13">
-        <v>1</v>
-      </c>
-      <c r="G44" s="13">
-        <v>1</v>
-      </c>
-      <c r="H44" s="15" t="s">
+      <c r="F44" s="10">
+        <v>1</v>
+      </c>
+      <c r="G44" s="10">
+        <v>1</v>
+      </c>
+      <c r="H44" s="12" t="s">
         <v>364</v>
       </c>
       <c r="I44" t="s">
@@ -4694,18 +5354,33 @@
       <c r="J44" t="s">
         <v>422</v>
       </c>
-      <c r="K44" s="10" t="s">
+      <c r="K44">
+        <v>0</v>
+      </c>
+      <c r="L44">
+        <v>1</v>
+      </c>
+      <c r="M44">
+        <v>0</v>
+      </c>
+      <c r="N44">
+        <v>0</v>
+      </c>
+      <c r="O44">
+        <v>0</v>
+      </c>
+      <c r="P44" s="8" t="s">
         <v>133</v>
       </c>
-      <c r="L44" s="9" t="s">
+      <c r="Q44" s="7" t="s">
         <v>428</v>
       </c>
     </row>
-    <row r="45" spans="1:12" ht="86.25">
-      <c r="A45" s="9" t="s">
+    <row r="45" spans="1:17" ht="86.25">
+      <c r="A45" s="7" t="s">
         <v>166</v>
       </c>
-      <c r="B45" s="10" t="s">
+      <c r="B45" s="8" t="s">
         <v>221</v>
       </c>
       <c r="C45" t="s">
@@ -4714,33 +5389,48 @@
       <c r="E45">
         <v>1</v>
       </c>
-      <c r="F45" s="13">
-        <v>1</v>
-      </c>
-      <c r="G45" s="13">
-        <v>0</v>
-      </c>
-      <c r="H45" s="15" t="s">
+      <c r="F45" s="10">
+        <v>1</v>
+      </c>
+      <c r="G45" s="10">
+        <v>0</v>
+      </c>
+      <c r="H45" s="12" t="s">
         <v>365</v>
       </c>
       <c r="I45" t="s">
         <v>375</v>
       </c>
-      <c r="J45" s="15" t="s">
+      <c r="J45" s="12" t="s">
         <v>423</v>
       </c>
-      <c r="K45" s="10" t="s">
+      <c r="K45">
+        <v>0</v>
+      </c>
+      <c r="L45">
+        <v>1</v>
+      </c>
+      <c r="M45">
+        <v>1</v>
+      </c>
+      <c r="N45">
+        <v>1</v>
+      </c>
+      <c r="O45">
+        <v>0</v>
+      </c>
+      <c r="P45" s="8" t="s">
         <v>134</v>
       </c>
-      <c r="L45" s="9" t="s">
+      <c r="Q45" s="7" t="s">
         <v>428</v>
       </c>
     </row>
-    <row r="46" spans="1:12" ht="72">
-      <c r="A46" s="9" t="s">
+    <row r="46" spans="1:17" ht="72">
+      <c r="A46" s="7" t="s">
         <v>167</v>
       </c>
-      <c r="B46" s="10" t="s">
+      <c r="B46" s="8" t="s">
         <v>222</v>
       </c>
       <c r="C46" t="s">
@@ -4749,33 +5439,48 @@
       <c r="E46">
         <v>1</v>
       </c>
-      <c r="F46" s="13">
-        <v>1</v>
-      </c>
-      <c r="G46" s="13">
-        <v>1</v>
-      </c>
-      <c r="H46" s="15" t="s">
+      <c r="F46" s="10">
+        <v>1</v>
+      </c>
+      <c r="G46" s="10">
+        <v>1</v>
+      </c>
+      <c r="H46" s="12" t="s">
         <v>353</v>
       </c>
       <c r="I46" t="s">
         <v>390</v>
       </c>
-      <c r="J46" s="15" t="s">
+      <c r="J46" s="12" t="s">
         <v>424</v>
       </c>
-      <c r="K46" s="10" t="s">
+      <c r="K46">
+        <v>1</v>
+      </c>
+      <c r="L46">
+        <v>0</v>
+      </c>
+      <c r="M46">
+        <v>1</v>
+      </c>
+      <c r="N46">
+        <v>0</v>
+      </c>
+      <c r="O46">
+        <v>0</v>
+      </c>
+      <c r="P46" s="8" t="s">
         <v>135</v>
       </c>
-      <c r="L46" s="9" t="s">
+      <c r="Q46" s="7" t="s">
         <v>428</v>
       </c>
     </row>
-    <row r="47" spans="1:12" ht="86.25">
-      <c r="A47" s="9" t="s">
+    <row r="47" spans="1:17" ht="86.25">
+      <c r="A47" s="7" t="s">
         <v>168</v>
       </c>
-      <c r="B47" s="10" t="s">
+      <c r="B47" s="8" t="s">
         <v>223</v>
       </c>
       <c r="C47" t="s">
@@ -4784,31 +5489,46 @@
       <c r="E47">
         <v>1</v>
       </c>
-      <c r="F47" s="13">
-        <v>0</v>
-      </c>
-      <c r="G47" s="13">
-        <v>0</v>
-      </c>
-      <c r="H47" s="15" t="s">
+      <c r="F47" s="10">
+        <v>0</v>
+      </c>
+      <c r="G47" s="10">
+        <v>0</v>
+      </c>
+      <c r="H47" s="12" t="s">
         <v>366</v>
       </c>
-      <c r="I47" s="16"/>
-      <c r="J47" s="15" t="s">
+      <c r="I47" s="13"/>
+      <c r="J47" s="12" t="s">
         <v>425</v>
       </c>
-      <c r="K47" s="10" t="s">
+      <c r="K47">
+        <v>1</v>
+      </c>
+      <c r="L47">
+        <v>0</v>
+      </c>
+      <c r="M47">
+        <v>1</v>
+      </c>
+      <c r="N47">
+        <v>1</v>
+      </c>
+      <c r="O47">
+        <v>0</v>
+      </c>
+      <c r="P47" s="8" t="s">
         <v>136</v>
       </c>
-      <c r="L47" s="9" t="s">
+      <c r="Q47" s="7" t="s">
         <v>428</v>
       </c>
     </row>
-    <row r="48" spans="1:12" ht="86.25">
-      <c r="A48" s="9" t="s">
+    <row r="48" spans="1:17" ht="86.25">
+      <c r="A48" s="7" t="s">
         <v>169</v>
       </c>
-      <c r="B48" s="10" t="s">
+      <c r="B48" s="8" t="s">
         <v>224</v>
       </c>
       <c r="C48" t="s">
@@ -4817,31 +5537,46 @@
       <c r="E48">
         <v>1</v>
       </c>
-      <c r="F48" s="13">
-        <v>1</v>
-      </c>
-      <c r="G48" s="13">
-        <v>0</v>
-      </c>
-      <c r="H48" s="15" t="s">
+      <c r="F48" s="10">
+        <v>1</v>
+      </c>
+      <c r="G48" s="10">
+        <v>0</v>
+      </c>
+      <c r="H48" s="12" t="s">
         <v>367</v>
       </c>
-      <c r="I48" s="12"/>
-      <c r="J48" s="15" t="s">
+      <c r="I48" s="9"/>
+      <c r="J48" s="12" t="s">
         <v>426</v>
       </c>
-      <c r="K48" s="10" t="s">
+      <c r="K48">
+        <v>1</v>
+      </c>
+      <c r="L48">
+        <v>1</v>
+      </c>
+      <c r="M48">
+        <v>1</v>
+      </c>
+      <c r="N48">
+        <v>0</v>
+      </c>
+      <c r="O48">
+        <v>0</v>
+      </c>
+      <c r="P48" s="8" t="s">
         <v>137</v>
       </c>
-      <c r="L48" s="9" t="s">
+      <c r="Q48" s="7" t="s">
         <v>428</v>
       </c>
     </row>
-    <row r="49" spans="1:12" ht="57.75">
-      <c r="A49" s="9" t="s">
+    <row r="49" spans="1:17" ht="57.75">
+      <c r="A49" s="7" t="s">
         <v>170</v>
       </c>
-      <c r="B49" s="10" t="s">
+      <c r="B49" s="8" t="s">
         <v>225</v>
       </c>
       <c r="C49" t="s">
@@ -4850,33 +5585,48 @@
       <c r="E49">
         <v>1</v>
       </c>
-      <c r="F49" s="13">
-        <v>1</v>
-      </c>
-      <c r="G49" s="13">
-        <v>0</v>
-      </c>
-      <c r="H49" s="15" t="s">
+      <c r="F49" s="10">
+        <v>1</v>
+      </c>
+      <c r="G49" s="10">
+        <v>0</v>
+      </c>
+      <c r="H49" s="12" t="s">
         <v>368</v>
       </c>
       <c r="I49" t="s">
         <v>375</v>
       </c>
-      <c r="J49" s="15" t="s">
+      <c r="J49" s="12" t="s">
         <v>427</v>
       </c>
-      <c r="K49" s="10" t="s">
+      <c r="K49">
+        <v>1</v>
+      </c>
+      <c r="L49">
+        <v>1</v>
+      </c>
+      <c r="M49">
+        <v>1</v>
+      </c>
+      <c r="N49">
+        <v>1</v>
+      </c>
+      <c r="O49">
+        <v>1</v>
+      </c>
+      <c r="P49" s="8" t="s">
         <v>138</v>
       </c>
-      <c r="L49" s="9" t="s">
+      <c r="Q49" s="7" t="s">
         <v>428</v>
       </c>
     </row>
-    <row r="50" spans="1:12" ht="51.75">
-      <c r="A50" s="9" t="s">
+    <row r="50" spans="1:17" ht="51.75">
+      <c r="A50" s="7" t="s">
         <v>171</v>
       </c>
-      <c r="B50" s="10" t="s">
+      <c r="B50" s="8" t="s">
         <v>226</v>
       </c>
       <c r="C50" t="s">
@@ -4885,39 +5635,54 @@
       <c r="E50">
         <v>1</v>
       </c>
-      <c r="F50" s="13">
-        <v>1</v>
-      </c>
-      <c r="G50" s="13">
-        <v>0</v>
-      </c>
-      <c r="H50" s="15" t="s">
+      <c r="F50" s="10">
+        <v>1</v>
+      </c>
+      <c r="G50" s="10">
+        <v>0</v>
+      </c>
+      <c r="H50" s="12" t="s">
         <v>351</v>
       </c>
       <c r="I50" t="s">
         <v>379</v>
       </c>
-      <c r="J50" s="15" t="s">
+      <c r="J50" s="12" t="s">
         <v>404</v>
       </c>
-      <c r="K50" s="10" t="s">
+      <c r="K50">
+        <v>1</v>
+      </c>
+      <c r="L50">
+        <v>1</v>
+      </c>
+      <c r="M50">
+        <v>0</v>
+      </c>
+      <c r="N50">
+        <v>0</v>
+      </c>
+      <c r="O50">
+        <v>0</v>
+      </c>
+      <c r="P50" s="8" t="s">
         <v>139</v>
       </c>
-      <c r="L50" s="9" t="s">
+      <c r="Q50" s="7" t="s">
         <v>428</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A1:L1"/>
-    <mergeCell ref="A2:L2"/>
+    <mergeCell ref="A1:Q1"/>
+    <mergeCell ref="A2:Q2"/>
   </mergeCells>
   <phoneticPr fontId="12" type="noConversion"/>
   <hyperlinks>
-    <hyperlink ref="K14" r:id="rId1" xr:uid="{EEEFE1CD-F3CB-4F36-85A1-6AD673E46BF8}"/>
-    <hyperlink ref="K16" r:id="rId2" xr:uid="{B16B6182-9666-4B03-A3C5-A9ABE678C54C}"/>
-    <hyperlink ref="K15" r:id="rId3" xr:uid="{42C0F240-BB1F-4FFA-A239-0FAE0BBD172B}"/>
-    <hyperlink ref="K17" r:id="rId4" xr:uid="{03F35E47-C051-4335-9ED1-EBC05DF8628E}"/>
+    <hyperlink ref="P14" r:id="rId1" xr:uid="{EEEFE1CD-F3CB-4F36-85A1-6AD673E46BF8}"/>
+    <hyperlink ref="P16" r:id="rId2" xr:uid="{B16B6182-9666-4B03-A3C5-A9ABE678C54C}"/>
+    <hyperlink ref="P15" r:id="rId3" xr:uid="{42C0F240-BB1F-4FFA-A239-0FAE0BBD172B}"/>
+    <hyperlink ref="P17" r:id="rId4" xr:uid="{03F35E47-C051-4335-9ED1-EBC05DF8628E}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="1">
@@ -4938,20 +5703,20 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" ht="30" customHeight="1">
-      <c r="A1" s="7" t="s">
+      <c r="A1" s="15" t="s">
         <v>65</v>
       </c>
-      <c r="B1" s="7"/>
-      <c r="C1" s="7"/>
-      <c r="D1" s="7"/>
+      <c r="B1" s="15"/>
+      <c r="C1" s="15"/>
+      <c r="D1" s="15"/>
     </row>
     <row r="2" spans="1:4" ht="33.950000000000003" customHeight="1">
-      <c r="A2" s="8" t="s">
+      <c r="A2" s="17" t="s">
         <v>66</v>
       </c>
-      <c r="B2" s="8"/>
-      <c r="C2" s="8"/>
-      <c r="D2" s="8"/>
+      <c r="B2" s="17"/>
+      <c r="C2" s="17"/>
+      <c r="D2" s="17"/>
     </row>
     <row r="3" spans="1:4" ht="36" customHeight="1">
       <c r="A3" s="1" t="s">
@@ -5108,512 +5873,512 @@
       </c>
     </row>
     <row r="14" spans="1:4" ht="409.5">
-      <c r="A14" s="10" t="s">
+      <c r="A14" s="8" t="s">
         <v>172</v>
       </c>
-      <c r="B14" s="10" t="s">
+      <c r="B14" s="8" t="s">
         <v>228</v>
       </c>
-      <c r="C14" s="10" t="s">
+      <c r="C14" s="8" t="s">
         <v>263</v>
       </c>
-      <c r="D14" s="10" t="s">
+      <c r="D14" s="8" t="s">
         <v>300</v>
       </c>
     </row>
     <row r="15" spans="1:4" ht="409.5">
-      <c r="A15" s="10" t="s">
+      <c r="A15" s="8" t="s">
         <v>173</v>
       </c>
-      <c r="B15" s="10" t="s">
+      <c r="B15" s="8" t="s">
         <v>229</v>
       </c>
-      <c r="C15" s="10" t="s">
+      <c r="C15" s="8" t="s">
         <v>264</v>
       </c>
-      <c r="D15" s="10" t="s">
+      <c r="D15" s="8" t="s">
         <v>301</v>
       </c>
     </row>
     <row r="16" spans="1:4" ht="409.5">
-      <c r="A16" s="10" t="s">
+      <c r="A16" s="8" t="s">
         <v>174</v>
       </c>
-      <c r="B16" s="10" t="s">
+      <c r="B16" s="8" t="s">
         <v>230</v>
       </c>
-      <c r="C16" s="10" t="s">
+      <c r="C16" s="8" t="s">
         <v>265</v>
       </c>
-      <c r="D16" s="10" t="s">
+      <c r="D16" s="8" t="s">
         <v>330</v>
       </c>
     </row>
     <row r="17" spans="1:4" ht="409.5">
-      <c r="A17" s="10" t="s">
+      <c r="A17" s="8" t="s">
         <v>175</v>
       </c>
-      <c r="B17" s="10" t="s">
+      <c r="B17" s="8" t="s">
         <v>231</v>
       </c>
-      <c r="C17" s="10" t="s">
+      <c r="C17" s="8" t="s">
         <v>266</v>
       </c>
-      <c r="D17" s="10" t="s">
+      <c r="D17" s="8" t="s">
         <v>302</v>
       </c>
     </row>
     <row r="18" spans="1:4" ht="369.75">
-      <c r="A18" s="10" t="s">
+      <c r="A18" s="8" t="s">
         <v>140</v>
       </c>
-      <c r="B18" s="10" t="s">
+      <c r="B18" s="8" t="s">
         <v>232</v>
       </c>
-      <c r="C18" s="10" t="s">
+      <c r="C18" s="8" t="s">
         <v>267</v>
       </c>
-      <c r="D18" s="10" t="s">
+      <c r="D18" s="8" t="s">
         <v>303</v>
       </c>
     </row>
     <row r="19" spans="1:4" ht="409.5">
-      <c r="A19" s="10" t="s">
+      <c r="A19" s="8" t="s">
         <v>176</v>
       </c>
-      <c r="B19" s="10" t="s">
+      <c r="B19" s="8" t="s">
         <v>233</v>
       </c>
-      <c r="C19" s="10" t="s">
+      <c r="C19" s="8" t="s">
         <v>268</v>
       </c>
-      <c r="D19" s="10" t="s">
+      <c r="D19" s="8" t="s">
         <v>304</v>
       </c>
     </row>
     <row r="20" spans="1:4" ht="293.25">
-      <c r="A20" s="10" t="s">
+      <c r="A20" s="8" t="s">
         <v>141</v>
       </c>
-      <c r="B20" s="10" t="s">
+      <c r="B20" s="8" t="s">
         <v>234</v>
       </c>
-      <c r="C20" s="10" t="s">
+      <c r="C20" s="8" t="s">
         <v>269</v>
       </c>
-      <c r="D20" s="10" t="s">
+      <c r="D20" s="8" t="s">
         <v>305</v>
       </c>
     </row>
     <row r="21" spans="1:4" ht="280.5">
-      <c r="A21" s="10" t="s">
+      <c r="A21" s="8" t="s">
         <v>142</v>
       </c>
-      <c r="B21" s="10" t="s">
+      <c r="B21" s="8" t="s">
         <v>235</v>
       </c>
-      <c r="C21" s="10" t="s">
+      <c r="C21" s="8" t="s">
         <v>270</v>
       </c>
-      <c r="D21" s="10" t="s">
+      <c r="D21" s="8" t="s">
         <v>306</v>
       </c>
     </row>
     <row r="22" spans="1:4" ht="408">
-      <c r="A22" s="10" t="s">
+      <c r="A22" s="8" t="s">
         <v>143</v>
       </c>
-      <c r="B22" s="10" t="s">
+      <c r="B22" s="8" t="s">
         <v>236</v>
       </c>
-      <c r="C22" s="10" t="s">
+      <c r="C22" s="8" t="s">
         <v>271</v>
       </c>
-      <c r="D22" s="10" t="s">
+      <c r="D22" s="8" t="s">
         <v>307</v>
       </c>
     </row>
     <row r="23" spans="1:4" ht="409.5">
-      <c r="A23" s="10" t="s">
+      <c r="A23" s="8" t="s">
         <v>144</v>
       </c>
-      <c r="B23" s="10" t="s">
+      <c r="B23" s="8" t="s">
         <v>237</v>
       </c>
-      <c r="C23" s="10" t="s">
+      <c r="C23" s="8" t="s">
         <v>272</v>
       </c>
-      <c r="D23" s="10" t="s">
+      <c r="D23" s="8" t="s">
         <v>308</v>
       </c>
     </row>
     <row r="24" spans="1:4" ht="357">
-      <c r="A24" s="10" t="s">
+      <c r="A24" s="8" t="s">
         <v>145</v>
       </c>
-      <c r="B24" s="10" t="s">
+      <c r="B24" s="8" t="s">
         <v>238</v>
       </c>
-      <c r="C24" s="10" t="s">
+      <c r="C24" s="8" t="s">
         <v>273</v>
       </c>
-      <c r="D24" s="10" t="s">
+      <c r="D24" s="8" t="s">
         <v>309</v>
       </c>
     </row>
     <row r="25" spans="1:4" ht="409.5">
-      <c r="A25" s="10" t="s">
+      <c r="A25" s="8" t="s">
         <v>146</v>
       </c>
-      <c r="B25" s="10" t="s">
+      <c r="B25" s="8" t="s">
         <v>239</v>
       </c>
-      <c r="C25" s="10" t="s">
+      <c r="C25" s="8" t="s">
         <v>274</v>
       </c>
-      <c r="D25" s="10" t="s">
+      <c r="D25" s="8" t="s">
         <v>310</v>
       </c>
     </row>
     <row r="26" spans="1:4" ht="409.5">
-      <c r="A26" s="10" t="s">
+      <c r="A26" s="8" t="s">
         <v>147</v>
       </c>
-      <c r="B26" s="10" t="s">
+      <c r="B26" s="8" t="s">
         <v>240</v>
       </c>
-      <c r="C26" s="10" t="s">
+      <c r="C26" s="8" t="s">
         <v>275</v>
       </c>
-      <c r="D26" s="10" t="s">
+      <c r="D26" s="8" t="s">
         <v>311</v>
       </c>
     </row>
     <row r="27" spans="1:4" ht="409.5">
-      <c r="A27" s="10" t="s">
+      <c r="A27" s="8" t="s">
         <v>148</v>
       </c>
-      <c r="B27" s="10" t="s">
+      <c r="B27" s="8" t="s">
         <v>241</v>
       </c>
-      <c r="C27" s="10" t="s">
+      <c r="C27" s="8" t="s">
         <v>276</v>
       </c>
-      <c r="D27" s="10" t="s">
+      <c r="D27" s="8" t="s">
         <v>312</v>
       </c>
     </row>
     <row r="28" spans="1:4" ht="395.25">
-      <c r="A28" s="10" t="s">
+      <c r="A28" s="8" t="s">
         <v>149</v>
       </c>
-      <c r="B28" s="10" t="s">
+      <c r="B28" s="8" t="s">
         <v>242</v>
       </c>
-      <c r="C28" s="10" t="s">
+      <c r="C28" s="8" t="s">
         <v>277</v>
       </c>
-      <c r="D28" s="10"/>
+      <c r="D28" s="8"/>
     </row>
     <row r="29" spans="1:4" ht="409.5">
-      <c r="A29" s="10" t="s">
+      <c r="A29" s="8" t="s">
         <v>150</v>
       </c>
-      <c r="B29" s="14" t="s">
+      <c r="B29" s="11" t="s">
         <v>243</v>
       </c>
-      <c r="C29" s="10" t="s">
+      <c r="C29" s="8" t="s">
         <v>278</v>
       </c>
-      <c r="D29" s="10"/>
+      <c r="D29" s="8"/>
     </row>
     <row r="30" spans="1:4" ht="409.5">
-      <c r="A30" s="10" t="s">
+      <c r="A30" s="8" t="s">
         <v>151</v>
       </c>
-      <c r="B30" s="10" t="s">
+      <c r="B30" s="8" t="s">
         <v>244</v>
       </c>
-      <c r="C30" s="10" t="s">
+      <c r="C30" s="8" t="s">
         <v>279</v>
       </c>
-      <c r="D30" s="10" t="s">
+      <c r="D30" s="8" t="s">
         <v>313</v>
       </c>
     </row>
     <row r="31" spans="1:4" ht="357">
-      <c r="A31" s="10" t="s">
+      <c r="A31" s="8" t="s">
         <v>152</v>
       </c>
-      <c r="B31" s="10" t="s">
+      <c r="B31" s="8" t="s">
         <v>245</v>
       </c>
-      <c r="C31" s="10" t="s">
+      <c r="C31" s="8" t="s">
         <v>280</v>
       </c>
-      <c r="D31" s="10" t="s">
+      <c r="D31" s="8" t="s">
         <v>314</v>
       </c>
     </row>
     <row r="32" spans="1:4" ht="409.5">
-      <c r="A32" s="10" t="s">
+      <c r="A32" s="8" t="s">
         <v>153</v>
       </c>
-      <c r="B32" s="10" t="s">
+      <c r="B32" s="8" t="s">
         <v>246</v>
       </c>
-      <c r="C32" s="10" t="s">
+      <c r="C32" s="8" t="s">
         <v>281</v>
       </c>
-      <c r="D32" s="10" t="s">
+      <c r="D32" s="8" t="s">
         <v>315</v>
       </c>
     </row>
     <row r="33" spans="1:4" ht="409.5">
-      <c r="A33" s="10" t="s">
+      <c r="A33" s="8" t="s">
         <v>154</v>
       </c>
-      <c r="B33" s="10" t="s">
+      <c r="B33" s="8" t="s">
         <v>247</v>
       </c>
-      <c r="C33" s="10" t="s">
+      <c r="C33" s="8" t="s">
         <v>282</v>
       </c>
-      <c r="D33" s="10" t="s">
+      <c r="D33" s="8" t="s">
         <v>316</v>
       </c>
     </row>
     <row r="34" spans="1:4" ht="409.5">
-      <c r="A34" s="10" t="s">
+      <c r="A34" s="8" t="s">
         <v>155</v>
       </c>
-      <c r="B34" s="10" t="s">
+      <c r="B34" s="8" t="s">
         <v>248</v>
       </c>
-      <c r="C34" s="10" t="s">
+      <c r="C34" s="8" t="s">
         <v>283</v>
       </c>
-      <c r="D34" s="10" t="s">
+      <c r="D34" s="8" t="s">
         <v>317</v>
       </c>
     </row>
     <row r="35" spans="1:4" ht="409.5">
-      <c r="A35" s="10" t="s">
+      <c r="A35" s="8" t="s">
         <v>156</v>
       </c>
-      <c r="B35" s="10" t="s">
+      <c r="B35" s="8" t="s">
         <v>249</v>
       </c>
-      <c r="C35" s="10" t="s">
+      <c r="C35" s="8" t="s">
         <v>284</v>
       </c>
-      <c r="D35" s="10" t="s">
+      <c r="D35" s="8" t="s">
         <v>318</v>
       </c>
     </row>
     <row r="36" spans="1:4" ht="331.5">
-      <c r="A36" s="10" t="s">
+      <c r="A36" s="8" t="s">
         <v>157</v>
       </c>
-      <c r="B36" s="10" t="s">
+      <c r="B36" s="8" t="s">
         <v>250</v>
       </c>
-      <c r="C36" s="10" t="s">
+      <c r="C36" s="8" t="s">
         <v>285</v>
       </c>
-      <c r="D36" s="10" t="s">
+      <c r="D36" s="8" t="s">
         <v>319</v>
       </c>
     </row>
     <row r="37" spans="1:4" ht="409.5">
-      <c r="A37" s="10" t="s">
+      <c r="A37" s="8" t="s">
         <v>158</v>
       </c>
-      <c r="B37" s="10" t="s">
+      <c r="B37" s="8" t="s">
         <v>251</v>
       </c>
-      <c r="C37" s="10" t="s">
+      <c r="C37" s="8" t="s">
         <v>286</v>
       </c>
-      <c r="D37" s="10" t="s">
+      <c r="D37" s="8" t="s">
         <v>310</v>
       </c>
     </row>
     <row r="38" spans="1:4" ht="409.5">
-      <c r="A38" s="10" t="s">
+      <c r="A38" s="8" t="s">
         <v>159</v>
       </c>
-      <c r="B38" s="10"/>
-      <c r="C38" s="10" t="s">
+      <c r="B38" s="8"/>
+      <c r="C38" s="8" t="s">
         <v>287</v>
       </c>
-      <c r="D38" s="10" t="s">
+      <c r="D38" s="8" t="s">
         <v>320</v>
       </c>
     </row>
     <row r="39" spans="1:4" ht="409.5">
-      <c r="A39" s="10" t="s">
+      <c r="A39" s="8" t="s">
         <v>160</v>
       </c>
-      <c r="B39" s="10" t="s">
+      <c r="B39" s="8" t="s">
         <v>252</v>
       </c>
-      <c r="C39" s="10" t="s">
+      <c r="C39" s="8" t="s">
         <v>288</v>
       </c>
-      <c r="D39" s="10" t="s">
+      <c r="D39" s="8" t="s">
         <v>321</v>
       </c>
     </row>
     <row r="40" spans="1:4" ht="255">
-      <c r="A40" s="10" t="s">
+      <c r="A40" s="8" t="s">
         <v>161</v>
       </c>
-      <c r="B40" s="10" t="s">
+      <c r="B40" s="8" t="s">
         <v>253</v>
       </c>
-      <c r="C40" s="10" t="s">
+      <c r="C40" s="8" t="s">
         <v>289</v>
       </c>
-      <c r="D40" s="10" t="s">
+      <c r="D40" s="8" t="s">
         <v>322</v>
       </c>
     </row>
     <row r="41" spans="1:4" ht="409.5">
-      <c r="A41" s="10" t="s">
+      <c r="A41" s="8" t="s">
         <v>162</v>
       </c>
-      <c r="B41" s="10" t="s">
+      <c r="B41" s="8" t="s">
         <v>254</v>
       </c>
-      <c r="C41" s="10" t="s">
+      <c r="C41" s="8" t="s">
         <v>290</v>
       </c>
-      <c r="D41" s="10" t="s">
+      <c r="D41" s="8" t="s">
         <v>310</v>
       </c>
     </row>
     <row r="42" spans="1:4" ht="409.5">
-      <c r="A42" s="10" t="s">
+      <c r="A42" s="8" t="s">
         <v>163</v>
       </c>
-      <c r="B42" s="10" t="s">
+      <c r="B42" s="8" t="s">
         <v>255</v>
       </c>
-      <c r="C42" s="10" t="s">
+      <c r="C42" s="8" t="s">
         <v>291</v>
       </c>
-      <c r="D42" s="10" t="s">
+      <c r="D42" s="8" t="s">
         <v>323</v>
       </c>
     </row>
     <row r="43" spans="1:4" ht="409.5">
-      <c r="A43" s="10" t="s">
+      <c r="A43" s="8" t="s">
         <v>164</v>
       </c>
-      <c r="B43" s="10" t="s">
+      <c r="B43" s="8" t="s">
         <v>256</v>
       </c>
-      <c r="C43" s="10" t="s">
+      <c r="C43" s="8" t="s">
         <v>292</v>
       </c>
-      <c r="D43" s="10" t="s">
+      <c r="D43" s="8" t="s">
         <v>324</v>
       </c>
     </row>
     <row r="44" spans="1:4" ht="409.5">
-      <c r="A44" s="10" t="s">
+      <c r="A44" s="8" t="s">
         <v>165</v>
       </c>
-      <c r="B44" s="10" t="s">
+      <c r="B44" s="8" t="s">
         <v>257</v>
       </c>
-      <c r="C44" s="10" t="s">
+      <c r="C44" s="8" t="s">
         <v>293</v>
       </c>
-      <c r="D44" s="10" t="s">
+      <c r="D44" s="8" t="s">
         <v>325</v>
       </c>
     </row>
     <row r="45" spans="1:4" ht="382.5">
-      <c r="A45" s="10" t="s">
+      <c r="A45" s="8" t="s">
         <v>166</v>
       </c>
-      <c r="B45" s="10" t="s">
+      <c r="B45" s="8" t="s">
         <v>258</v>
       </c>
-      <c r="C45" s="10" t="s">
+      <c r="C45" s="8" t="s">
         <v>294</v>
       </c>
-      <c r="D45" s="10" t="s">
+      <c r="D45" s="8" t="s">
         <v>326</v>
       </c>
     </row>
     <row r="46" spans="1:4" ht="409.5">
-      <c r="A46" s="10" t="s">
+      <c r="A46" s="8" t="s">
         <v>167</v>
       </c>
-      <c r="B46" s="10" t="s">
+      <c r="B46" s="8" t="s">
         <v>259</v>
       </c>
-      <c r="C46" s="10" t="s">
+      <c r="C46" s="8" t="s">
         <v>295</v>
       </c>
-      <c r="D46" s="10" t="s">
+      <c r="D46" s="8" t="s">
         <v>327</v>
       </c>
     </row>
     <row r="47" spans="1:4" ht="127.5">
-      <c r="A47" s="10" t="s">
+      <c r="A47" s="8" t="s">
         <v>168</v>
       </c>
-      <c r="B47" s="10" t="s">
+      <c r="B47" s="8" t="s">
         <v>260</v>
       </c>
-      <c r="C47" s="10" t="s">
+      <c r="C47" s="8" t="s">
         <v>296</v>
       </c>
-      <c r="D47" s="10" t="s">
+      <c r="D47" s="8" t="s">
         <v>328</v>
       </c>
     </row>
     <row r="48" spans="1:4" ht="229.5">
-      <c r="A48" s="10" t="s">
+      <c r="A48" s="8" t="s">
         <v>169</v>
       </c>
-      <c r="B48" s="10" t="s">
+      <c r="B48" s="8" t="s">
         <v>261</v>
       </c>
-      <c r="C48" s="10" t="s">
+      <c r="C48" s="8" t="s">
         <v>297</v>
       </c>
-      <c r="D48" s="10"/>
+      <c r="D48" s="8"/>
     </row>
     <row r="49" spans="1:4" ht="409.5">
-      <c r="A49" s="10" t="s">
+      <c r="A49" s="8" t="s">
         <v>170</v>
       </c>
-      <c r="B49" s="10" t="s">
+      <c r="B49" s="8" t="s">
         <v>262</v>
       </c>
-      <c r="C49" s="10" t="s">
+      <c r="C49" s="8" t="s">
         <v>298</v>
       </c>
-      <c r="D49" s="10" t="s">
+      <c r="D49" s="8" t="s">
         <v>329</v>
       </c>
     </row>
     <row r="50" spans="1:4" ht="409.5">
-      <c r="A50" s="10" t="s">
+      <c r="A50" s="8" t="s">
         <v>171</v>
       </c>
-      <c r="B50" s="10" t="s">
+      <c r="B50" s="8" t="s">
         <v>240</v>
       </c>
-      <c r="C50" s="10" t="s">
+      <c r="C50" s="8" t="s">
         <v>299</v>
       </c>
-      <c r="D50" s="10" t="s">
+      <c r="D50" s="8" t="s">
         <v>311</v>
       </c>
     </row>
